--- a/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/5.2-organic-fertiliser.xlsx
+++ b/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/5.2-organic-fertiliser.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A836D426-8FF4-FC4C-B07E-8DC15B969A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DDB057-6A1B-264D-8A1F-29B353BEE7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="28800" windowHeight="15900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.2.1.1 (purchased_untraced)" sheetId="1" r:id="rId1"/>
@@ -19,6 +14,9 @@
     <sheet name="5.2.1.1 (dairy)" sheetId="9" r:id="rId4"/>
     <sheet name="5.2.1.1 (poultry)" sheetId="5" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1908,6 +1906,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2256,8 +2279,8 @@
         <v>3</v>
       </c>
       <c r="O11">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -2326,11 +2349,11 @@
       </c>
       <c r="K17">
         <f t="shared" ref="K17:K22" si="3">IF(ISBLANK(B17), "", $O$11)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="L17">
         <f t="shared" ref="L17:L22" si="4">IF(ISBLANK(B17), "", I17*J17*K17 / 1000)</f>
-        <v>4.8085714285714285E-3</v>
+        <v>4.8042000000000007E-3</v>
       </c>
       <c r="N17" t="s">
         <v>17</v>
@@ -2363,11 +2386,11 @@
       </c>
       <c r="K18">
         <f t="shared" si="3"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="L18">
         <f t="shared" si="4"/>
-        <v>5.6571428571428571E-3</v>
+        <v>5.6519999999999999E-3</v>
       </c>
       <c r="N18" t="s">
         <v>18</v>
@@ -2397,11 +2420,11 @@
       </c>
       <c r="K19">
         <f t="shared" si="3"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="L19">
         <f t="shared" si="4"/>
-        <v>4.0071428571428567E-3</v>
+        <v>4.003500000000001E-3</v>
       </c>
       <c r="N19" t="s">
         <v>20</v>
@@ -2434,11 +2457,11 @@
       </c>
       <c r="K20">
         <f t="shared" si="3"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="L20">
         <f t="shared" si="4"/>
-        <v>5.4685714285714298E-4</v>
+        <v>5.4636000000000007E-4</v>
       </c>
       <c r="N20" t="s">
         <v>21</v>
@@ -2471,11 +2494,11 @@
       </c>
       <c r="K21">
         <f t="shared" si="3"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="L21">
         <f t="shared" si="4"/>
-        <v>7.7785714285714285E-4</v>
+        <v>7.7715E-4</v>
       </c>
       <c r="N21" t="s">
         <v>15</v>
@@ -2511,11 +2534,11 @@
       </c>
       <c r="K22">
         <f t="shared" si="3"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="L22">
         <f t="shared" si="4"/>
-        <v>5.6571428571428571E-4</v>
+        <v>5.6520000000000008E-4</v>
       </c>
       <c r="N22" t="s">
         <v>23</v>
@@ -2587,7 +2610,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A6:O43" numberStoredAsText="1"/>
+    <ignoredError sqref="A6:O10 A12:O43 A11:N11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3489,15 +3512,15 @@
       </c>
       <c r="CU8">
         <f>IF(ISBLANK(A8), "", $CZ$12)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV8">
         <f>IF(ISBLANK(A8), "", CS8*CT8*CU8 / 1000)</f>
-        <v>2.0672985920400003E-3</v>
+        <v>2.0654192296836005E-3</v>
       </c>
       <c r="CW8">
         <f>SUM(CV8:CV11)</f>
-        <v>4.8337585345254855E-2</v>
+        <v>4.8293642085850089E-2</v>
       </c>
       <c r="CY8" t="s">
         <v>1</v>
@@ -3765,11 +3788,11 @@
       </c>
       <c r="CU9">
         <f t="shared" ref="CU9:CU23" si="51">IF(ISBLANK(A8), "", $CZ$12)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV9">
         <f t="shared" ref="CV9:CV23" si="52">IF(ISBLANK(A8), "", CS9*CT9*CU9 / 1000)</f>
-        <v>4.3203544488719997E-3</v>
+        <v>4.316426853918481E-3</v>
       </c>
       <c r="CY9" t="s">
         <v>2</v>
@@ -4028,11 +4051,11 @@
       </c>
       <c r="CU10">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV10">
         <f t="shared" si="52"/>
-        <v>1.5890998237714286E-2</v>
+        <v>1.587655187568E-2</v>
       </c>
     </row>
     <row r="11" spans="1:104" x14ac:dyDescent="0.2">
@@ -4312,11 +4335,11 @@
       </c>
       <c r="CU11">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV11">
         <f t="shared" si="52"/>
-        <v>2.6058934066628573E-2</v>
+        <v>2.6035244126568002E-2</v>
       </c>
     </row>
     <row r="12" spans="1:104" x14ac:dyDescent="0.2">
@@ -4640,22 +4663,22 @@
       </c>
       <c r="CU12">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV12">
         <f t="shared" si="52"/>
-        <v>7.0402721322656257E-4</v>
+        <v>7.0338718848726581E-4</v>
       </c>
       <c r="CW12">
         <f>SUM(CV12:CV15)</f>
-        <v>1.9102857705182233E-2</v>
+        <v>1.9085491470904797E-2</v>
       </c>
       <c r="CY12" t="s">
         <v>3</v>
       </c>
       <c r="CZ12">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="13" spans="1:104" x14ac:dyDescent="0.2">
@@ -4979,11 +5002,11 @@
       </c>
       <c r="CU13">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV13">
         <f t="shared" si="52"/>
-        <v>6.7661436618015637E-3</v>
+        <v>6.7599926221090165E-3</v>
       </c>
       <c r="CY13" t="s">
         <v>55</v>
@@ -5313,11 +5336,11 @@
       </c>
       <c r="CU14">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV14">
         <f t="shared" si="52"/>
-        <v>1.0863922152545001E-2</v>
+        <v>1.0854045859679053E-2</v>
       </c>
       <c r="CY14" t="s">
         <v>307</v>
@@ -5653,11 +5676,11 @@
       </c>
       <c r="CU15">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV15">
         <f t="shared" si="52"/>
-        <v>7.6876467760910729E-4</v>
+        <v>7.6806580062946264E-4</v>
       </c>
     </row>
     <row r="16" spans="1:104" x14ac:dyDescent="0.2">
@@ -5927,15 +5950,15 @@
       </c>
       <c r="CU16">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV16">
         <f t="shared" si="52"/>
-        <v>2.4132383314285719E-2</v>
+        <v>2.4110444784000006E-2</v>
       </c>
       <c r="CW16">
         <f>SUM(CV16:CV19)</f>
-        <v>4.4676487872342865E-2</v>
+        <v>4.4635872883368004E-2</v>
       </c>
     </row>
     <row r="17" spans="1:104" x14ac:dyDescent="0.2">
@@ -6205,11 +6228,11 @@
       </c>
       <c r="CU17">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV17">
         <f t="shared" si="52"/>
-        <v>5.989552615199999E-3</v>
+        <v>5.9841075673679996E-3</v>
       </c>
     </row>
     <row r="18" spans="1:104" x14ac:dyDescent="0.2">
@@ -6465,11 +6488,11 @@
       </c>
       <c r="CU18">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV18">
         <f t="shared" si="52"/>
-        <v>1.3364125570714286E-2</v>
+        <v>1.3351976365650001E-2</v>
       </c>
       <c r="CY18" t="s">
         <v>17</v>
@@ -6754,11 +6777,11 @@
       </c>
       <c r="CU19">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV19">
         <f t="shared" si="52"/>
-        <v>1.1904263721428572E-3</v>
+        <v>1.1893441663500001E-3</v>
       </c>
       <c r="CY19" t="s">
         <v>18</v>
@@ -7073,15 +7096,15 @@
       </c>
       <c r="CU20">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV20">
         <f t="shared" si="52"/>
-        <v>2.2962215394642858E-2</v>
+        <v>2.2941340653375001E-2</v>
       </c>
       <c r="CW20">
         <f>SUM(CV20:CV23)</f>
-        <v>5.8610371705547948E-2</v>
+        <v>5.8557089549451997E-2</v>
       </c>
       <c r="CY20" t="s">
         <v>20</v>
@@ -7399,11 +7422,11 @@
       </c>
       <c r="CU21">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV21">
         <f t="shared" si="52"/>
-        <v>1.1967919425000001E-2</v>
+        <v>1.1957039498250001E-2</v>
       </c>
       <c r="CY21" t="s">
         <v>21</v>
@@ -7721,11 +7744,11 @@
       </c>
       <c r="CU22">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV22">
         <f t="shared" si="52"/>
-        <v>4.8333466639366067E-3</v>
+        <v>4.8289527124239368E-3</v>
       </c>
       <c r="CY22" t="s">
         <v>15</v>
@@ -8053,11 +8076,11 @@
       </c>
       <c r="CU23">
         <f t="shared" si="51"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CV23">
         <f t="shared" si="52"/>
-        <v>1.8846890221968483E-2</v>
+        <v>1.8829756685403057E-2</v>
       </c>
       <c r="CY23" t="s">
         <v>23</v>
@@ -8718,11 +8741,11 @@
       </c>
       <c r="AG8">
         <f t="shared" ref="AG8:AG15" si="15">IF(ISBLANK(K8), "", $AK$12)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AH8">
         <f t="shared" ref="AH8:AH15" si="16">IF(ISBLANK(K8), "", AE8*AF8*AG8/1000)</f>
-        <v>1.9940795237902632E-2</v>
+        <v>1.9922667242231813E-2</v>
       </c>
       <c r="AJ8" t="s">
         <v>1</v>
@@ -8845,11 +8868,11 @@
       </c>
       <c r="AG9">
         <f t="shared" si="15"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AH9">
         <f t="shared" si="16"/>
-        <v>1.6617329364918859E-2</v>
+        <v>1.6602222701859844E-2</v>
       </c>
       <c r="AJ9" t="s">
         <v>2</v>
@@ -8972,11 +8995,11 @@
       </c>
       <c r="AG10">
         <f t="shared" si="15"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AH10">
         <f t="shared" si="16"/>
-        <v>1.5976695381021259E-2</v>
+        <v>1.5962171112493061E-2</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.2">
@@ -9093,11 +9116,11 @@
       </c>
       <c r="AG11">
         <f t="shared" si="15"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AH11">
         <f t="shared" si="16"/>
-        <v>1.9940795237902632E-2</v>
+        <v>1.9922667242231813E-2</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.2">
@@ -9214,18 +9237,18 @@
       </c>
       <c r="AG12">
         <f t="shared" si="15"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AH12">
         <f t="shared" si="16"/>
-        <v>1.9940795237902632E-2</v>
+        <v>1.9922667242231813E-2</v>
       </c>
       <c r="AJ12" t="s">
         <v>3</v>
       </c>
       <c r="AK12">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.2">
@@ -9342,11 +9365,11 @@
       </c>
       <c r="AG13">
         <f t="shared" si="15"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AH13">
         <f t="shared" si="16"/>
-        <v>1.9940795237902632E-2</v>
+        <v>1.9922667242231813E-2</v>
       </c>
       <c r="AJ13" t="s">
         <v>55</v>
@@ -9469,11 +9492,11 @@
       </c>
       <c r="AG14">
         <f t="shared" si="15"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AH14">
         <f t="shared" si="16"/>
-        <v>1.9940795237902632E-2</v>
+        <v>1.9922667242231813E-2</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.2">
@@ -9590,11 +9613,11 @@
       </c>
       <c r="AG15">
         <f t="shared" si="15"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AH15">
         <f t="shared" si="16"/>
-        <v>1.9940795237902632E-2</v>
+        <v>1.9922667242231813E-2</v>
       </c>
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.2">
@@ -9714,11 +9737,11 @@
       </c>
       <c r="AG21">
         <f>IF(ISBLANK(K21), "", $AK$12)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AH21">
         <f>IF(ISBLANK(K21), "", AE21*AF21*AG21/1000)</f>
-        <v>1.8648336287297829E-2</v>
+        <v>1.863138325430938E-2</v>
       </c>
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.2">
@@ -9838,11 +9861,11 @@
       </c>
       <c r="AG22">
         <f>IF(ISBLANK(K22), "", $AK$12)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="AH22">
         <f>IF(ISBLANK(K22), "", AE22*AF22*AG22/1000)</f>
-        <v>2.2433394642640467E-2</v>
+        <v>2.2413000647510794E-2</v>
       </c>
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.2">
@@ -9954,7 +9977,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AE7 A8:C8 E8 J8:M8 X8 AD8 O8:R8 AK30:AL33 U8:V8 AF1:AH8 A18:AH20 AI34:AL44 AI30:AI33 AI1:AL29 A23:AH44" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AE7 A8:C8 E8 J8:M8 X8 AD8 O8:R8 AK30:AL33 U8:V8 AF1:AH8 A18:AH20 AI34:AL44 AI30:AI33 AI1:AL11 A23:AH44 AI13:AL29 AI12:AJ12 AL12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -10581,7 +10604,7 @@
       </c>
       <c r="CC8">
         <f>$B$123</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CD8">
         <f>SUM(BW8:BZ8)*CA8</f>
@@ -10589,7 +10612,7 @@
       </c>
       <c r="CE8">
         <f>CD8*$CC8*$CB8/1000</f>
-        <v>8.8052000160264099E-2</v>
+        <v>8.7971952887391139E-2</v>
       </c>
     </row>
     <row r="9" spans="1:83" x14ac:dyDescent="0.2">
@@ -10875,7 +10898,7 @@
       </c>
       <c r="CC9">
         <f t="shared" ref="CC9:CC63" si="53">$B$123</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="10" spans="1:83" x14ac:dyDescent="0.2">
@@ -11161,7 +11184,7 @@
       </c>
       <c r="CC10">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="11" spans="1:83" x14ac:dyDescent="0.2">
@@ -11447,7 +11470,7 @@
       </c>
       <c r="CC11">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="12" spans="1:83" x14ac:dyDescent="0.2">
@@ -11733,7 +11756,7 @@
       </c>
       <c r="CC12">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="13" spans="1:83" x14ac:dyDescent="0.2">
@@ -12019,7 +12042,7 @@
       </c>
       <c r="CC13">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="14" spans="1:83" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -12305,7 +12328,7 @@
       </c>
       <c r="CC14" s="3">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="15" spans="1:83" x14ac:dyDescent="0.2">
@@ -12600,7 +12623,7 @@
       </c>
       <c r="CC15">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CD15">
         <f>SUM(BW15:BZ15)*CA15</f>
@@ -12608,7 +12631,7 @@
       </c>
       <c r="CE15">
         <f>CD15*$CC15*$CB15/1000</f>
-        <v>6.1286519803002378E-2</v>
+        <v>6.1230804784999655E-2</v>
       </c>
     </row>
     <row r="16" spans="1:83" x14ac:dyDescent="0.2">
@@ -12894,7 +12917,7 @@
       </c>
       <c r="CC16">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="17" spans="1:83" x14ac:dyDescent="0.2">
@@ -13180,7 +13203,7 @@
       </c>
       <c r="CC17">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="18" spans="1:83" x14ac:dyDescent="0.2">
@@ -13466,7 +13489,7 @@
       </c>
       <c r="CC18">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="19" spans="1:83" x14ac:dyDescent="0.2">
@@ -13752,7 +13775,7 @@
       </c>
       <c r="CC19">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="20" spans="1:83" x14ac:dyDescent="0.2">
@@ -14038,7 +14061,7 @@
       </c>
       <c r="CC20">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="21" spans="1:83" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -14324,7 +14347,7 @@
       </c>
       <c r="CC21" s="3">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="22" spans="1:83" x14ac:dyDescent="0.2">
@@ -14619,7 +14642,7 @@
       </c>
       <c r="CC22">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CD22">
         <f t="shared" ref="CD22" si="86">SUM(BW22:BZ22)*CA22</f>
@@ -14627,7 +14650,7 @@
       </c>
       <c r="CE22">
         <f t="shared" ref="CE22" si="87">CD22*$CC22*$CB22/1000</f>
-        <v>0.22700031661263198</v>
+        <v>0.22679395268843866</v>
       </c>
     </row>
     <row r="23" spans="1:83" x14ac:dyDescent="0.2">
@@ -14916,7 +14939,7 @@
       </c>
       <c r="CC23">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="24" spans="1:83" x14ac:dyDescent="0.2">
@@ -15205,7 +15228,7 @@
       </c>
       <c r="CC24">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="25" spans="1:83" x14ac:dyDescent="0.2">
@@ -15494,7 +15517,7 @@
       </c>
       <c r="CC25">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="26" spans="1:83" x14ac:dyDescent="0.2">
@@ -15783,7 +15806,7 @@
       </c>
       <c r="CC26">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="27" spans="1:83" x14ac:dyDescent="0.2">
@@ -16072,7 +16095,7 @@
       </c>
       <c r="CC27">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="28" spans="1:83" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -16361,7 +16384,7 @@
       </c>
       <c r="CC28" s="3">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="29" spans="1:83" x14ac:dyDescent="0.2">
@@ -16656,7 +16679,7 @@
       </c>
       <c r="CC29">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CD29">
         <f t="shared" ref="CD29" si="88">SUM(BW29:BZ29)*CA29</f>
@@ -16664,7 +16687,7 @@
       </c>
       <c r="CE29">
         <f t="shared" ref="CE29" si="89">CD29*$CC29*$CB29/1000</f>
-        <v>1.8403862071772355E-2</v>
+        <v>1.8387131288070745E-2</v>
       </c>
     </row>
     <row r="30" spans="1:83" x14ac:dyDescent="0.2">
@@ -16953,7 +16976,7 @@
       </c>
       <c r="CC30">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="31" spans="1:83" x14ac:dyDescent="0.2">
@@ -17242,7 +17265,7 @@
       </c>
       <c r="CC31">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="32" spans="1:83" x14ac:dyDescent="0.2">
@@ -17531,7 +17554,7 @@
       </c>
       <c r="CC32">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="33" spans="1:83" x14ac:dyDescent="0.2">
@@ -17820,7 +17843,7 @@
       </c>
       <c r="CC33">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="34" spans="1:83" x14ac:dyDescent="0.2">
@@ -18109,7 +18132,7 @@
       </c>
       <c r="CC34">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="35" spans="1:83" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -18398,7 +18421,7 @@
       </c>
       <c r="CC35" s="3">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="36" spans="1:83" x14ac:dyDescent="0.2">
@@ -18687,7 +18710,7 @@
       </c>
       <c r="CC36">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CD36">
         <f t="shared" ref="CD36" si="117">SUM(BW36:BZ36)*CA36</f>
@@ -18695,7 +18718,7 @@
       </c>
       <c r="CE36">
         <f t="shared" ref="CE36" si="118">CD36*$CC36*$CB36/1000</f>
-        <v>0.10635694886241849</v>
+        <v>0.10626026072708901</v>
       </c>
     </row>
     <row r="37" spans="1:83" x14ac:dyDescent="0.2">
@@ -18984,7 +19007,7 @@
       </c>
       <c r="CC37">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="38" spans="1:83" x14ac:dyDescent="0.2">
@@ -19273,7 +19296,7 @@
       </c>
       <c r="CC38">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="39" spans="1:83" x14ac:dyDescent="0.2">
@@ -19562,7 +19585,7 @@
       </c>
       <c r="CC39">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="40" spans="1:83" x14ac:dyDescent="0.2">
@@ -19851,7 +19874,7 @@
       </c>
       <c r="CC40">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="41" spans="1:83" x14ac:dyDescent="0.2">
@@ -20140,7 +20163,7 @@
       </c>
       <c r="CC41">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="42" spans="1:83" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -20429,7 +20452,7 @@
       </c>
       <c r="CC42" s="3">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="43" spans="1:83" x14ac:dyDescent="0.2">
@@ -20724,7 +20747,7 @@
       </c>
       <c r="CC43">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CD43">
         <f>SUM(BW43:BZ43)*CA43</f>
@@ -20732,7 +20755,7 @@
       </c>
       <c r="CE43">
         <f>CD43*$CC43*$CB43/1000</f>
-        <v>6.8469455467961043E-2</v>
+        <v>6.8407210508444699E-2</v>
       </c>
     </row>
     <row r="44" spans="1:83" x14ac:dyDescent="0.2">
@@ -21021,7 +21044,7 @@
       </c>
       <c r="CC44">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="45" spans="1:83" x14ac:dyDescent="0.2">
@@ -21310,7 +21333,7 @@
       </c>
       <c r="CC45">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="46" spans="1:83" x14ac:dyDescent="0.2">
@@ -21599,7 +21622,7 @@
       </c>
       <c r="CC46">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="47" spans="1:83" x14ac:dyDescent="0.2">
@@ -21888,7 +21911,7 @@
       </c>
       <c r="CC47">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="48" spans="1:83" x14ac:dyDescent="0.2">
@@ -22177,7 +22200,7 @@
       </c>
       <c r="CC48">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="49" spans="1:83" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -22466,7 +22489,7 @@
       </c>
       <c r="CC49" s="3">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="50" spans="1:83" x14ac:dyDescent="0.2">
@@ -22761,7 +22784,7 @@
       </c>
       <c r="CC50">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CD50">
         <f>SUM(BW50:BZ50)*CA50</f>
@@ -22769,7 +22792,7 @@
       </c>
       <c r="CE50">
         <f>CD50*$CC50*$CB50/1000</f>
-        <v>2.7877701422827757E-2</v>
+        <v>2.7852358057897909E-2</v>
       </c>
     </row>
     <row r="51" spans="1:83" x14ac:dyDescent="0.2">
@@ -23058,7 +23081,7 @@
       </c>
       <c r="CC51">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="52" spans="1:83" x14ac:dyDescent="0.2">
@@ -23347,7 +23370,7 @@
       </c>
       <c r="CC52">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="53" spans="1:83" x14ac:dyDescent="0.2">
@@ -23636,7 +23659,7 @@
       </c>
       <c r="CC53">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="54" spans="1:83" x14ac:dyDescent="0.2">
@@ -23925,7 +23948,7 @@
       </c>
       <c r="CC54">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="55" spans="1:83" x14ac:dyDescent="0.2">
@@ -24214,7 +24237,7 @@
       </c>
       <c r="CC55">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="56" spans="1:83" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -24503,7 +24526,7 @@
       </c>
       <c r="CC56" s="3">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="57" spans="1:83" x14ac:dyDescent="0.2">
@@ -24792,7 +24815,7 @@
       </c>
       <c r="CC57">
         <f>$B$123</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="CD57">
         <f>SUM(BW57:BZ57)*CA57</f>
@@ -24800,7 +24823,7 @@
       </c>
       <c r="CE57">
         <f>CD57*$CC57*$CB57/1000</f>
-        <v>9.4585561442785487E-2</v>
+        <v>9.4499574568746608E-2</v>
       </c>
     </row>
     <row r="58" spans="1:83" x14ac:dyDescent="0.2">
@@ -25089,7 +25112,7 @@
       </c>
       <c r="CC58">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="59" spans="1:83" x14ac:dyDescent="0.2">
@@ -25378,7 +25401,7 @@
       </c>
       <c r="CC59">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="60" spans="1:83" x14ac:dyDescent="0.2">
@@ -25667,7 +25690,7 @@
       </c>
       <c r="CC60">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="61" spans="1:83" x14ac:dyDescent="0.2">
@@ -25956,7 +25979,7 @@
       </c>
       <c r="CC61">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="62" spans="1:83" x14ac:dyDescent="0.2">
@@ -26245,7 +26268,7 @@
       </c>
       <c r="CC62">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="63" spans="1:83" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -26534,7 +26557,7 @@
       </c>
       <c r="CC63" s="3">
         <f t="shared" si="53"/>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.2">
@@ -27869,8 +27892,8 @@
         <v>454</v>
       </c>
       <c r="B123">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.2">
@@ -28694,11 +28717,11 @@
       </c>
       <c r="BT11" s="32">
         <f>IF(ISBLANK(D11), "", $BX$16)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BU11" s="32">
         <f>IF(ISBLANK(D11), "", BR11*BS11*BT11/1000)</f>
-        <v>2.4342648018872825E-3</v>
+        <v>2.4320518338855671E-3</v>
       </c>
       <c r="CB11" s="35" t="s">
         <v>194</v>
@@ -29374,8 +29397,8 @@
         <v>3</v>
       </c>
       <c r="BX16" s="32">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
       <c r="CB16" s="35" t="s">
         <v>197</v>
@@ -29618,11 +29641,11 @@
       </c>
       <c r="BT21" s="32">
         <f>IF(ISBLANK(D21), "", $BX$16)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BU21" s="32">
         <f>IF(ISBLANK(D21), "", BR21*BS21*BT21/1000)</f>
-        <v>2.4349533783788319E-3</v>
+        <v>2.4327397843984877E-3</v>
       </c>
       <c r="BW21" s="32" t="s">
         <v>235</v>
@@ -29838,7 +29861,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="23" spans="1:80" ht="32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:80" ht="48" x14ac:dyDescent="0.2">
       <c r="B23" s="32">
         <v>0.6</v>
       </c>
@@ -30573,11 +30596,11 @@
       </c>
       <c r="BT31" s="32">
         <f>IF(ISBLANK(D31), "", $BX$16)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BU31" s="32">
         <f>IF(ISBLANK(D31), "", BR31*BS31*BT31/1000)</f>
-        <v>2.0285540015727356E-3</v>
+        <v>2.0267098615713059E-3</v>
       </c>
       <c r="BW31" s="32" t="s">
         <v>240</v>
@@ -31511,11 +31534,11 @@
       </c>
       <c r="BT41" s="32">
         <f>IF(ISBLANK(D41), "", $BX$16)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BU41" s="32">
         <f>IF(ISBLANK(D41), "", BR41*BS41*BT41/1000)</f>
-        <v>1.4709875625597806E-3</v>
+        <v>1.4696503011392716E-3</v>
       </c>
     </row>
     <row r="42" spans="1:77" x14ac:dyDescent="0.2">
@@ -32361,11 +32384,11 @@
       </c>
       <c r="BT51" s="32">
         <f>IF(ISBLANK(D51), "", $BX$16)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BU51" s="32">
         <f>IF(ISBLANK(D51), "", BR51*BS51*BT51/1000)</f>
-        <v>3.2287827090671179E-3</v>
+        <v>3.2258474520588751E-3</v>
       </c>
     </row>
     <row r="52" spans="1:73" x14ac:dyDescent="0.2">
